--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484328_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484328_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3978</v>
+        <v>5.4199</v>
       </c>
       <c r="E2" t="n">
-        <v>7.217</v>
+        <v>6.2664</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8192</v>
+        <v>-0.8465</v>
       </c>
       <c r="G2" t="n">
         <v>3.3528</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9669</v>
+        <v>-0.011</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1282</v>
+        <v>0.1776</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1613</v>
+        <v>-0.1886</v>
       </c>
       <c r="V2" t="n">
         <v>1.8828</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0304</v>
+        <v>4.9174</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1895</v>
+        <v>5.5939</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1591</v>
+        <v>-0.6766</v>
       </c>
       <c r="G3" t="n">
         <v>5.2218</v>
@@ -688,13 +688,13 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0742</v>
+        <v>-1.1872</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.392</v>
+        <v>-0.9876</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3178</v>
+        <v>-0.1996</v>
       </c>
       <c r="V3" t="n">
         <v>1.2735</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9158</v>
+        <v>3.5109</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3643</v>
+        <v>5.7687</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4484</v>
+        <v>-2.2578</v>
       </c>
       <c r="G4" t="n">
         <v>3.0292</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5291</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2105</v>
+        <v>-0.806</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3187</v>
+        <v>-0.128</v>
       </c>
       <c r="V4" t="n">
         <v>0.2437</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8116</v>
+        <v>1.0489</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1129</v>
+        <v>1.214</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3012</v>
+        <v>-0.165</v>
       </c>
       <c r="G5" t="n">
         <v>1.6663</v>
@@ -844,13 +844,13 @@
         <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6025</v>
+        <v>-0.3652</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4237</v>
+        <v>-0.3225</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1789</v>
+        <v>-0.0427</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6428</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4918</v>
+        <v>-1.3634</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1935</v>
+        <v>-0.0924</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2983</v>
+        <v>-1.271</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6448</v>
@@ -922,13 +922,13 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6284</v>
+        <v>-0.5</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3863</v>
+        <v>-0.3591</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8844</v>
+        <v>-1.4777</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4162</v>
+        <v>2.5779</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3007</v>
+        <v>-4.0556</v>
       </c>
       <c r="G7" t="n">
         <v>1.2251</v>
@@ -1000,13 +1000,13 @@
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1764</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5915</v>
+        <v>-0.4298</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.585</v>
+        <v>-0.3399</v>
       </c>
       <c r="V7" t="n">
         <v>-2.7145</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0575</v>
+        <v>-1.8064</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1676</v>
+        <v>0.2281</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2252</v>
+        <v>-2.0345</v>
       </c>
       <c r="G8" t="n">
         <v>-3.6396</v>
@@ -1078,13 +1078,13 @@
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3062</v>
+        <v>-1.0551</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.22</v>
+        <v>-0.1594</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0863</v>
+        <v>-0.8956</v>
       </c>
       <c r="V8" t="n">
         <v>1.1303</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5853</v>
+        <v>-3.035</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5378</v>
+        <v>-0.6088</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0474</v>
+        <v>-2.4262</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4894</v>
+        <v>-2.5768</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9381</v>
+        <v>-1.9033</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5513</v>
+        <v>-0.6735</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7765</v>
+        <v>-0.5299</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3047</v>
+        <v>-0.5308</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4718</v>
+        <v>0.001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7129</v>
+        <v>-2.047</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6334</v>
+        <v>-1.3725</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0795</v>
+        <v>-0.6745</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4185</v>
+        <v>-0.4367</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6962</v>
+        <v>-0.079</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7223000000000001</v>
+        <v>-0.3577</v>
       </c>
       <c r="V9" t="n">
-        <v>0.853</v>
+        <v>-1.5842</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6428</v>
+        <v>-1.5842</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1033</v>
+        <v>-3.75</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5683</v>
+        <v>-2.1851</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5351</v>
+        <v>-1.5649</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5768</v>
+        <v>-3.4894</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9033</v>
+        <v>-1.9381</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6735</v>
+        <v>-1.5513</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5299</v>
+        <v>-1.7765</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5308</v>
+        <v>-1.3047</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001</v>
+        <v>-0.4718</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.047</v>
+        <v>-1.7129</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3725</v>
+        <v>-0.6334</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6745</v>
+        <v>-1.0795</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5627</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5051</v>
+        <v>0.2538</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0384</v>
+        <v>0.0489</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4667</v>
+        <v>0.2048</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5842</v>
+        <v>0.853</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5842</v>
+        <v>-0.6428</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4302</v>
+        <v>-3.9712</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5611</v>
+        <v>-1.1566</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8691</v>
+        <v>-2.8146</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6445</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7037</v>
+        <v>-0.2448</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6052</v>
+        <v>-0.2008</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7614</v>
+        <v>-4.3492</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5964</v>
+        <v>-0.293</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.165</v>
+        <v>-4.0561</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5668</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.4037</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3318</v>
+        <v>-0.2229</v>
       </c>
       <c r="V12" t="n">
         <v>-2.16</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.158300000000001</v>
+        <v>-4.855800000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0104</v>
+        <v>17.3131</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.1687</v>
+        <v>-22.1688</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0667</v>
@@ -1438,7 +1438,7 @@
         <v>-4.417899999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1.351200000000001</v>
+        <v>1.3512</v>
       </c>
       <c r="J13" t="n">
         <v>19.4543</v>
@@ -1459,7 +1459,7 @@
         <v>-10.7945</v>
       </c>
       <c r="P13" t="n">
-        <v>5.860299999999999</v>
+        <v>5.8603</v>
       </c>
       <c r="Q13" t="n">
         <v>-7.8136</v>
@@ -1468,16 +1468,16 @@
         <v>13.6742</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.956199999999998</v>
+        <v>-5.653599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3832</v>
+        <v>-3.0804</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5734</v>
+        <v>-2.5733</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.995400000000001</v>
+        <v>-1.9954</v>
       </c>
       <c r="W13" t="n">
         <v>8.752800000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3537</v>
+        <v>4.2876</v>
       </c>
       <c r="E14" t="n">
-        <v>8.168699999999999</v>
+        <v>7.9665</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8151</v>
+        <v>-3.6789</v>
       </c>
       <c r="G14" t="n">
         <v>-0.549</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8336</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5752</v>
+        <v>0.3729</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3245</v>
+        <v>0.4607</v>
       </c>
       <c r="V14" t="n">
         <v>5.7611</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3046</v>
+        <v>4.2307</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9985</v>
+        <v>4.8973</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6938</v>
+        <v>-0.6666</v>
       </c>
       <c r="G15" t="n">
         <v>1.9978</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6509</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2642</v>
+        <v>0.1631</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3867</v>
+        <v>0.414</v>
       </c>
       <c r="V15" t="n">
         <v>2.4373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3574</v>
+        <v>3.2468</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7631</v>
+        <v>4.4709</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4057</v>
+        <v>-1.2241</v>
       </c>
       <c r="G16" t="n">
         <v>5.389</v>
@@ -1702,13 +1702,13 @@
         <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0232</v>
+        <v>0.9126</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>0.9916</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8828</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5778</v>
+        <v>1.1807</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9509</v>
+        <v>2.2543</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3731</v>
+        <v>-1.0736</v>
       </c>
       <c r="G17" t="n">
         <v>1.7846</v>
@@ -1780,13 +1780,13 @@
         <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7027</v>
+        <v>-0.0998</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3631</v>
+        <v>-0.0598</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3396</v>
+        <v>-0.04</v>
       </c>
       <c r="V17" t="n">
         <v>0.2772</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3281</v>
+        <v>0.1481</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0991</v>
+        <v>1.6524</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4272</v>
+        <v>-1.5043</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0225</v>
+        <v>-0.7817</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0412</v>
+        <v>0.1215</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0638</v>
+        <v>-0.9033</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5696</v>
+        <v>1.4012</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1489</v>
+        <v>0.8199</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5794</v>
+        <v>0.5813</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5921</v>
+        <v>-2.183</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1077</v>
+        <v>-0.6984</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4844</v>
+        <v>-1.4846</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9717</v>
+        <v>0.4257</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5063</v>
+        <v>0.2512</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4654</v>
+        <v>0.1746</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4193</v>
+        <v>-0.2399</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8089</v>
+        <v>0.998</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2282</v>
+        <v>-1.2379</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8634</v>
+        <v>-1.0225</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3118</v>
+        <v>1.0412</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5515</v>
+        <v>-2.0638</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6538</v>
+        <v>1.5696</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4515</v>
+        <v>2.1489</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2023</v>
+        <v>-0.5794</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5172</v>
+        <v>-2.5921</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7634</v>
+        <v>-1.1077</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7538</v>
+        <v>-1.4844</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1901</v>
+        <v>1.0599</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8545</v>
+        <v>0.4052</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3356</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4807</v>
+        <v>-1.4305</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3491</v>
+        <v>0.7977</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8297</v>
+        <v>-2.2282</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7817</v>
+        <v>-1.8634</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1215</v>
+        <v>-0.3118</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9033</v>
+        <v>-1.5515</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4012</v>
+        <v>0.6538</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8199</v>
+        <v>0.4515</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5813</v>
+        <v>0.2023</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.183</v>
+        <v>-2.5172</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6984</v>
+        <v>-0.7634</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4846</v>
+        <v>-1.7538</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2031</v>
+        <v>1.1789</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0522</v>
+        <v>0.8434</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1509</v>
+        <v>0.3356</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>-0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5603</v>
+        <v>-2.7185</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2853</v>
+        <v>0.7809</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2751</v>
+        <v>-3.4994</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6787</v>
+        <v>0.6156</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6805</v>
+        <v>-0.5308</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9982</v>
+        <v>1.1465</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5103</v>
+        <v>3.2776</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9171</v>
+        <v>0.7815</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5931999999999999</v>
+        <v>2.496</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1684</v>
+        <v>-2.6619</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7634</v>
+        <v>-1.3123</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4051</v>
+        <v>-1.3496</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6458</v>
+        <v>0.5839</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9245</v>
+        <v>0.1562</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.4277</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9414</v>
+        <v>-2.16</v>
       </c>
       <c r="W22" t="n">
         <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8219</v>
+        <v>-3.0479</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2753</v>
+        <v>-1.6897</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0972</v>
+        <v>-1.3582</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6156</v>
+        <v>-2.6787</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5308</v>
+        <v>-1.6805</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1465</v>
+        <v>-0.9982</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2776</v>
+        <v>-1.5103</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7815</v>
+        <v>-0.9171</v>
       </c>
       <c r="L23" t="n">
-        <v>2.496</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6619</v>
+        <v>-1.1684</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3123</v>
+        <v>-0.7634</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3496</v>
+        <v>-0.4051</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5195</v>
+        <v>1.1583</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3494</v>
+        <v>0.5201</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1701</v>
+        <v>0.6382</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.16</v>
+        <v>-0.9414</v>
       </c>
       <c r="W23" t="n">
         <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.158500000000002</v>
+        <v>5.8324</v>
       </c>
       <c r="E24" t="n">
         <v>22.1688</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.0103</v>
+        <v>-16.3364</v>
       </c>
       <c r="G24" t="n">
-        <v>3.067000000000001</v>
+        <v>3.067</v>
       </c>
       <c r="H24" t="n">
         <v>4.418099999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3513</v>
+        <v>-1.351300000000001</v>
       </c>
       <c r="J24" t="n">
         <v>22.5213</v>
@@ -2311,7 +2311,7 @@
         <v>-19.4543</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.3087</v>
+        <v>-7.308700000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-12.1457</v>
@@ -2323,19 +2323,19 @@
         <v>-13.6738</v>
       </c>
       <c r="R24" t="n">
-        <v>7.8139</v>
+        <v>7.813899999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>5.9561</v>
+        <v>6.6302</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5732</v>
+        <v>2.5733</v>
       </c>
       <c r="U24" t="n">
-        <v>3.382900000000001</v>
+        <v>4.0571</v>
       </c>
       <c r="V24" t="n">
-        <v>1.9956</v>
+        <v>1.995599999999999</v>
       </c>
       <c r="W24" t="n">
         <v>10.7481</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484328_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484328_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5109</v>
+        <v>2.1279</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7687</v>
+        <v>2.1279</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2578</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0292</v>
+        <v>2.1279</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4751</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5541</v>
+        <v>1.821</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9654</v>
+        <v>2.1279</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1967</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7686</v>
+        <v>1.821</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9362</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7217</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2146</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9340000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.806</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.128</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2437</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3656</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>R. GUARDIOLA I DISPES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0489</v>
+        <v>1.383</v>
       </c>
       <c r="E5" t="n">
-        <v>1.214</v>
+        <v>3.6408</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.165</v>
+        <v>-2.2578</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6663</v>
+        <v>0.9012</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4646</v>
+        <v>2.1681</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1309</v>
+        <v>-1.2669</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5365</v>
+        <v>3.8375</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3249</v>
+        <v>3.8898</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8614</v>
+        <v>-0.0523</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1298</v>
+        <v>-2.9362</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1397</v>
+        <v>-1.7217</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2694</v>
+        <v>-1.2146</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3652</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3225</v>
+        <v>-0.806</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0427</v>
+        <v>-0.128</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6428</v>
+        <v>0.2437</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6428</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3634</v>
+        <v>1.0489</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0924</v>
+        <v>1.214</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.271</v>
+        <v>-0.165</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6448</v>
+        <v>1.6663</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2829</v>
+        <v>-0.4646</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3618</v>
+        <v>2.1309</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0486</v>
+        <v>1.5365</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0614</v>
+        <v>-0.3249</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0128</v>
+        <v>1.8614</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6933</v>
+        <v>0.1298</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3443</v>
+        <v>-0.1397</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.349</v>
+        <v>0.2694</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5</v>
+        <v>-0.3652</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.141</v>
+        <v>-0.3225</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3591</v>
+        <v>-0.0427</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6428</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +985,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4777</v>
+        <v>-1.3634</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5779</v>
+        <v>-0.0924</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0556</v>
+        <v>-1.271</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2251</v>
+        <v>-1.6448</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1353</v>
+        <v>-0.2829</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3604</v>
+        <v>-1.3618</v>
       </c>
       <c r="J7" t="n">
-        <v>3.0077</v>
+        <v>0.0486</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1625</v>
+        <v>0.0614</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1701</v>
+        <v>-0.0128</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7826</v>
+        <v>-1.6933</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9729</v>
+        <v>-0.3443</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8097</v>
+        <v>-1.349</v>
       </c>
       <c r="P7" t="n">
         <v>0.7814</v>
@@ -1000,28 +1030,33 @@
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4298</v>
+        <v>-0.141</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3399</v>
+        <v>-0.3591</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8064</v>
+        <v>-1.4777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2281</v>
+        <v>2.5779</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0345</v>
+        <v>-4.0556</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6396</v>
+        <v>1.2251</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1929</v>
+        <v>-1.1353</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5533</v>
+        <v>2.3604</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1083</v>
+        <v>3.0077</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.4713</v>
+        <v>-0.1625</v>
       </c>
       <c r="L8" t="n">
-        <v>1.363</v>
+        <v>3.1701</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5314</v>
+        <v>-1.7826</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7217</v>
+        <v>-0.9729</v>
       </c>
       <c r="O8" t="n">
         <v>-0.8097</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0551</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1594</v>
+        <v>-0.4298</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8956</v>
+        <v>-0.3399</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1303</v>
+        <v>-2.7145</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3656</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.035</v>
+        <v>-1.8064</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6088</v>
+        <v>0.2281</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4262</v>
+        <v>-2.0345</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5768</v>
+        <v>-3.6396</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9033</v>
+        <v>-4.1929</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6735</v>
+        <v>0.5533</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5299</v>
+        <v>-1.1083</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5308</v>
+        <v>-2.4713</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001</v>
+        <v>1.363</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.047</v>
+        <v>-2.5314</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3725</v>
+        <v>-1.7217</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6745</v>
+        <v>-0.8097</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4367</v>
+        <v>-1.0551</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.079</v>
+        <v>-0.1594</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3577</v>
+        <v>-0.8956</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5842</v>
+        <v>1.1303</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5842</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.75</v>
+        <v>-3.035</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1851</v>
+        <v>-0.6088</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5649</v>
+        <v>-2.4262</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4894</v>
+        <v>-2.5768</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9381</v>
+        <v>-1.9033</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5513</v>
+        <v>-0.6735</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7765</v>
+        <v>-0.5299</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3047</v>
+        <v>-0.5308</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4718</v>
+        <v>0.001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7129</v>
+        <v>-2.047</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6334</v>
+        <v>-1.3725</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0795</v>
+        <v>-0.6745</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2538</v>
+        <v>-0.4367</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0489</v>
+        <v>-0.079</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2048</v>
+        <v>-0.3577</v>
       </c>
       <c r="V10" t="n">
-        <v>0.853</v>
+        <v>-1.5842</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6428</v>
+        <v>-1.5842</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9712</v>
+        <v>-3.75</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1566</v>
+        <v>-2.1851</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8146</v>
+        <v>-1.5649</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6445</v>
+        <v>-3.4894</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9189</v>
+        <v>-1.9381</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7256</v>
+        <v>-1.5513</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1978</v>
+        <v>-1.7765</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5513</v>
+        <v>-1.3047</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6465</v>
+        <v>-0.4718</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4468</v>
+        <v>-1.7129</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3676</v>
+        <v>-0.6334</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0792</v>
+        <v>-1.0795</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2448</v>
+        <v>0.2538</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2008</v>
+        <v>0.0489</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.044</v>
+        <v>0.2048</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>0.853</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4959</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3492</v>
+        <v>-3.9712</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.293</v>
+        <v>-1.1566</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0561</v>
+        <v>-2.8146</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5668</v>
+        <v>-3.6445</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6493</v>
+        <v>-1.9189</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9175</v>
+        <v>-1.7256</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3894</v>
+        <v>-1.1978</v>
       </c>
       <c r="K12" t="n">
         <v>-0.5513</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1619</v>
+        <v>-0.6465</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1773</v>
+        <v>-2.4468</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.098</v>
+        <v>-1.3676</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0793</v>
+        <v>-1.0792</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4037</v>
+        <v>-0.2448</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1808</v>
+        <v>-0.2008</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2229</v>
+        <v>-0.044</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.855800000000002</v>
+        <v>-4.3492</v>
       </c>
       <c r="E13" t="n">
-        <v>17.3131</v>
+        <v>-0.293</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.1688</v>
+        <v>-4.0561</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0667</v>
+        <v>-2.5668</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.417899999999999</v>
+        <v>-1.6493</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3512</v>
+        <v>-0.9175</v>
       </c>
       <c r="J13" t="n">
-        <v>19.4543</v>
+        <v>-0.3894</v>
       </c>
       <c r="K13" t="n">
-        <v>7.3087</v>
+        <v>-0.5513</v>
       </c>
       <c r="L13" t="n">
-        <v>12.1455</v>
+        <v>0.1619</v>
       </c>
       <c r="M13" t="n">
-        <v>-22.5211</v>
+        <v>-2.1773</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.7268</v>
+        <v>-1.098</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.7945</v>
+        <v>-1.0793</v>
       </c>
       <c r="P13" t="n">
-        <v>5.8603</v>
+        <v>0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.8136</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6742</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.653599999999999</v>
+        <v>-0.4037</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0804</v>
+        <v>-0.1808</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.5733</v>
+        <v>-0.2229</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9954</v>
+        <v>-2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>8.752800000000001</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.7483</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>CB QUART GRUES CRUZ</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2876</v>
+        <v>-4.855800000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9665</v>
+        <v>17.3131</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.6789</v>
+        <v>-22.1688</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.549</v>
+        <v>-3.066800000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0228</v>
+        <v>-4.4179</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5263</v>
+        <v>1.351200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6574</v>
+        <v>19.4543</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2944</v>
+        <v>7.308800000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>1.363</v>
+        <v>12.1456</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2065</v>
+        <v>-22.5211</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3172</v>
+        <v>-11.7268</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8893</v>
+        <v>-10.7945</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7581</v>
+        <v>5.860299999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-7.8136</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>13.6742</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8336</v>
+        <v>-5.6536</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3729</v>
+        <v>-3.0804</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4607</v>
+        <v>-2.5733</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7611</v>
+        <v>-1.995400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8662</v>
+        <v>8.752800000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1052</v>
-      </c>
+        <v>-10.7483</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2307</v>
+        <v>4.2876</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8973</v>
+        <v>7.9665</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6666</v>
+        <v>-3.6789</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9978</v>
+        <v>-0.549</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8115</v>
+        <v>-0.0228</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1863</v>
+        <v>-0.5263</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2504</v>
+        <v>2.6574</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5797</v>
+        <v>1.2944</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6707</v>
+        <v>1.363</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2526</v>
+        <v>-3.2065</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7682</v>
+        <v>-1.3172</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4844</v>
+        <v>-1.8893</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.8336</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1631</v>
+        <v>0.3729</v>
       </c>
       <c r="U15" t="n">
-        <v>0.414</v>
+        <v>0.4607</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4373</v>
+        <v>5.7611</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>7.8662</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2468</v>
+        <v>4.2307</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4709</v>
+        <v>4.8973</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2241</v>
+        <v>-0.6666</v>
       </c>
       <c r="G16" t="n">
-        <v>5.389</v>
+        <v>1.9978</v>
       </c>
       <c r="H16" t="n">
-        <v>3.461</v>
+        <v>0.8115</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9279</v>
+        <v>1.1863</v>
       </c>
       <c r="J16" t="n">
-        <v>7.1675</v>
+        <v>4.2504</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8898</v>
+        <v>1.5797</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2777</v>
+        <v>2.6707</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7785</v>
+        <v>-2.2526</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4287</v>
+        <v>-0.7682</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3498</v>
+        <v>-1.4844</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9126</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.079</v>
+        <v>0.1631</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9916</v>
+        <v>0.414</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8828</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6642</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1807</v>
+        <v>3.2468</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2543</v>
+        <v>4.4709</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0736</v>
+        <v>-1.2241</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7846</v>
+        <v>5.389</v>
       </c>
       <c r="H17" t="n">
-        <v>1.394</v>
+        <v>3.461</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3906</v>
+        <v>1.9279</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0136</v>
+        <v>7.1675</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6782</v>
+        <v>3.8898</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3354</v>
+        <v>3.2777</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2289</v>
+        <v>-1.7785</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2842</v>
+        <v>-0.4287</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9447</v>
+        <v>-1.3498</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0998</v>
+        <v>0.9126</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0598</v>
+        <v>-0.079</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.04</v>
+        <v>0.9916</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2772</v>
+        <v>-1.8828</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. PÉREZ CARRASCO</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1894,72 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1753</v>
+        <v>1.1807</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0405</v>
+        <v>2.2543</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1348</v>
+        <v>-1.0736</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1753</v>
+        <v>1.7846</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1348</v>
+        <v>1.394</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0405</v>
+        <v>0.3906</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0405</v>
+        <v>3.0136</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.6782</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>1.3354</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1348</v>
+        <v>-1.2289</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1348</v>
+        <v>-0.2842</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.9447</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.0998</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0598</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1481</v>
+        <v>0.914</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6524</v>
+        <v>0.914</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5043</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7817</v>
+        <v>0.914</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1215</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9033</v>
+        <v>0.607</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4012</v>
+        <v>0.914</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8199</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5813</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.183</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6984</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4846</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4257</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2512</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1746</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>F. PEREZ CARRASCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2399</v>
+        <v>0.1753</v>
       </c>
       <c r="E20" t="n">
-        <v>0.998</v>
+        <v>0.0405</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2379</v>
+        <v>0.1348</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0225</v>
+        <v>0.1753</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0412</v>
+        <v>0.1348</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0638</v>
+        <v>0.0405</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5696</v>
+        <v>0.0405</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1489</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5794</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5921</v>
+        <v>0.1348</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1077</v>
+        <v>0.1348</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4844</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0599</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4052</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6546999999999999</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4305</v>
+        <v>-0.2399</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7977</v>
+        <v>0.998</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2282</v>
+        <v>-1.2379</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8634</v>
+        <v>-1.0225</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3118</v>
+        <v>1.0412</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5515</v>
+        <v>-2.0638</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6538</v>
+        <v>1.5696</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4515</v>
+        <v>2.1489</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2023</v>
+        <v>-0.5794</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5172</v>
+        <v>-2.5921</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7634</v>
+        <v>-1.1077</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7538</v>
+        <v>-1.4844</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1789</v>
+        <v>1.0599</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8434</v>
+        <v>0.4052</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3356</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7185</v>
+        <v>-0.7658</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7809</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4994</v>
+        <v>-1.5043</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6156</v>
+        <v>-1.6957</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5308</v>
+        <v>-0.1855</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1465</v>
+        <v>-1.5103</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2776</v>
+        <v>0.4873</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7815</v>
+        <v>0.5129</v>
       </c>
       <c r="L22" t="n">
-        <v>2.496</v>
+        <v>-0.0257</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6619</v>
+        <v>-2.183</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3123</v>
+        <v>-0.6984</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3496</v>
+        <v>-1.4846</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5839</v>
+        <v>0.4257</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1562</v>
+        <v>0.2512</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4277</v>
+        <v>0.1746</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0479</v>
+        <v>-1.4305</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6897</v>
+        <v>0.7977</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3582</v>
+        <v>-2.2282</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6787</v>
+        <v>-1.8634</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6805</v>
+        <v>-0.3118</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9982</v>
+        <v>-1.5515</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5103</v>
+        <v>0.6538</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9171</v>
+        <v>0.4515</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.2023</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1684</v>
+        <v>-2.5172</v>
       </c>
       <c r="N23" t="n">
         <v>-0.7634</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4051</v>
+        <v>-1.7538</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1583</v>
+        <v>1.1789</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5201</v>
+        <v>0.8434</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6382</v>
+        <v>0.3356</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9414</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.8324</v>
+        <v>-2.7185</v>
       </c>
       <c r="E24" t="n">
+        <v>0.7809</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-3.4994</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.5308</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.1465</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.2776</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2.496</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.6619</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.3123</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.3496</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.5839</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M. SALMERON SEGU</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.0479</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.6897</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.3582</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.6787</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.6805</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.9982</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.5103</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.9171</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.1684</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.7634</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.1583</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5201</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484328_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5.8325</v>
+      </c>
+      <c r="E26" t="n">
         <v>22.1688</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-16.3364</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>3.067</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>4.418099999999998</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>-1.351300000000001</v>
       </c>
-      <c r="J24" t="n">
-        <v>22.5213</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J26" t="n">
+        <v>22.5214</v>
+      </c>
+      <c r="K26" t="n">
         <v>11.7268</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>10.7943</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-19.4543</v>
       </c>
-      <c r="N24" t="n">
-        <v>-7.308700000000001</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N26" t="n">
+        <v>-7.308699999999999</v>
+      </c>
+      <c r="O26" t="n">
         <v>-12.1457</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-5.8604</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-13.6738</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>7.813899999999999</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>6.6302</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>2.5733</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>4.0571</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>1.995599999999999</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>10.7481</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-8.752700000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
